--- a/data/trans_bre/P1435_2011_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1435_2011_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,62</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>340,12%</t>
+          <t>341,59%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,51</t>
+          <t>2,11; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 11,28</t>
+          <t>5,95; 10,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218,49; 2011,32</t>
+          <t>191,58; 1873,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167,44; 690,69</t>
+          <t>161,14; 697,59</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,94</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1086,48%</t>
+          <t>492,68%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,17</t>
+          <t>2,24; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 38,36</t>
+          <t>5,86; 8,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>466,32; 4067,12</t>
+          <t>442,39; 3564,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367,73; 4428,8</t>
+          <t>264,19; 781,32</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363,43%</t>
+          <t>327,73%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,81</t>
+          <t>1,82; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,98</t>
+          <t>4,42; 8,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154,8; 779,4</t>
+          <t>155,12; 640,96</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,23</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>745,31%</t>
+          <t>426,16%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,99</t>
+          <t>2,58; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 28,71</t>
+          <t>6,3; 8,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520,93; 2137,84</t>
+          <t>535,43; 2297,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384,65; 1933,13</t>
+          <t>295,11; 612,03</t>
         </is>
       </c>
     </row>
